--- a/main/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T07:00:21+00:00</t>
+    <t>2026-08-04T07:50:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T07:50:37+00:00</t>
+    <t>2026-08-04T08:17:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$114</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3219" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4226" uniqueCount="596">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T08:17:33+00:00</t>
+    <t>2026-08-06T12:56:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -661,13 +661,322 @@
 booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
   </si>
   <si>
-    <t>ServiceRequest.modifierExtension</t>
+    <t>ServiceRequest.extension:reason</t>
+  </si>
+  <si>
+    <t>reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-ServiceRequest.reason|0.1.0}
+</t>
+  </si>
+  <si>
+    <t>R5: Explanation/Justification for procedure or service additional types</t>
+  </si>
+  <si>
+    <t>R5: `ServiceRequest.reason` additional types (CodeableReference(http://hl7.org/fhir/StructureDefinition/Condition), CodeableReference(http://hl7.org/fhir/StructureDefinition/Observation), CodeableReference(http://hl7.org/fhir/StructureDefinition/DiagnosticReport), CodeableReference(http://hl7.org/fhir/StructureDefinition/DocumentReference), CodeableReference(http://hl7.org/fhir/StructureDefinition/DetectedIssue))</t>
+  </si>
+  <si>
+    <t>Element `ServiceRequest.reason` is mapped to FHIR R4 element `ServiceRequest.reasonCode` as `SourceIsBroaderThanTarget`.
+Element `ServiceRequest.reason` is mapped to FHIR R4 element `ServiceRequest.reasonReference` as `SourceIsBroaderThanTarget`.
+The mappings for `ServiceRequest.reason` do not cover the following types: CodeableReference.
+This element represents why the referral is being made and may be used to decide how the service will be performed, or even if it will be performed at all. To be as specific as possible,  a reference to  *Observation* or *Condition* should be used if available.  Otherwise, use `concept.text` element if the data is free (uncoded) text as shown in the [CT Scan example](https://hl7.org/fhir/servicerequest-example-di.html).</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/finaliteExamen</t>
+  </si>
+  <si>
+    <t>reason/finaliteExamen</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/finaliteExamen.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/finaliteExamen.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/finaliteExamen.extension:_datatype</t>
+  </si>
+  <si>
+    <t>_datatype</t>
+  </si>
+  <si>
+    <t>DataType slice for a FHIR R5 `CodeableReference` value</t>
+  </si>
+  <si>
+    <t>Slice to indicate the presence of a R5 `CodeableReference` in FHIR R4</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/finaliteExamen.extension:_datatype.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/finaliteExamen.extension:_datatype.extension</t>
   </si>
   <si>
     <t>extensions
 user content</t>
   </si>
   <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/finaliteExamen.extension:_datatype.url</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/_datatype</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/finaliteExamen.extension:_datatype.value[x]</t>
+  </si>
+  <si>
+    <t>Must be: CodeableReference</t>
+  </si>
+  <si>
+    <t>CodeableReference</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/finaliteExamen.extension:concept</t>
+  </si>
+  <si>
+    <t>concept</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/finaliteExamen.extension:concept.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/finaliteExamen.extension:concept.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/finaliteExamen.extension:concept.url</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/finaliteExamen.extension:concept.value[x]</t>
+  </si>
+  <si>
+    <t>Reference to a concept (by class)</t>
+  </si>
+  <si>
+    <t>A reference to a concept - e.g. the information is identified by its general class to the degree of precision found in the terminology.</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/document-core/CodeSystem/fr-cs-note-type"/&gt;
+    &lt;code value="finaliteExamen"/&gt;
+    &lt;display value="Finalité de l'examen"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/finaliteExamen.extension:concept.value[x].id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension.extension.value[x].id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/finaliteExamen.extension:concept.value[x].extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension.extension.value[x].extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/finaliteExamen.extension:concept.value[x].coding</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension.extension.value[x].coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/finaliteExamen.extension:concept.value[x].text</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension.extension.value[x].text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/finaliteExamen.extension:reference</t>
+  </si>
+  <si>
+    <t>reference</t>
+  </si>
+  <si>
+    <t>R5: Reference to a resource (by instance)</t>
+  </si>
+  <si>
+    <t>R5: `CodeableReference.reference`</t>
+  </si>
+  <si>
+    <t>Element `CodeableReference.reference` is mapped to FHIR R4 element `Reference` as `Equivalent`.</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/finaliteExamen.extension:reference.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/finaliteExamen.extension:reference.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/finaliteExamen.extension:reference.url</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/finaliteExamen.extension:reference.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/5.0/StructureDefinition/profile-Condition|0.1.0|Condition|4.0.1|http://hl7.org/fhir/5.0/StructureDefinition/profile-Observation|0.1.0|Observation|4.0.1|http://hl7.org/fhir/5.0/StructureDefinition/profile-DiagnosticReport|0.1.0|DiagnosticReport|4.0.1|http://hl7.org/fhir/5.0/StructureDefinition/profile-DocumentReference-for-Media|0.1.0|Media|4.0.1|http://hl7.org/fhir/5.0/StructureDefinition/profile-DetectedIssue|0.1.0|DetectedIssue|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Reference to a resource (by instance)</t>
+  </si>
+  <si>
+    <t>A reference to a resource the provides exact details about the information being referenced.</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/finaliteExamen.url</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/5.0/StructureDefinition/extension-ServiceRequest.reason</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/finaliteExamen.value[x]</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/justificationDemande</t>
+  </si>
+  <si>
+    <t>reason/justificationDemande</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/justificationDemande.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/justificationDemande.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/justificationDemande.extension:_datatype</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/justificationDemande.extension:_datatype.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/justificationDemande.extension:_datatype.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/justificationDemande.extension:_datatype.url</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/justificationDemande.extension:_datatype.value[x]</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/justificationDemande.extension:concept</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/justificationDemande.extension:concept.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/justificationDemande.extension:concept.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/justificationDemande.extension:concept.url</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/justificationDemande.extension:concept.value[x]</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/document-core/CodeSystem/fr-cs-note-type"/&gt;
+    &lt;code value="justificationDemande"/&gt;
+    &lt;display value="Justification de la demande"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/justificationDemande.extension:concept.value[x].id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/justificationDemande.extension:concept.value[x].extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/justificationDemande.extension:concept.value[x].coding</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/justificationDemande.extension:concept.value[x].text</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/justificationDemande.extension:reference</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/justificationDemande.extension:reference.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/justificationDemande.extension:reference.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/justificationDemande.extension:reference.url</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/justificationDemande.extension:reference.value[x]</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/justificationDemande.url</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:reason/justificationDemande.value[x]</t>
+  </si>
+  <si>
+    <t>ServiceRequest.modifierExtension</t>
+  </si>
+  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -675,9 +984,6 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -1535,10 +1841,6 @@
     <t>Any other notes and comments made about the service request. For example, internal billing notes.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:extension('http://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-note-type-extension')}
-</t>
-  </si>
-  <si>
     <t>Request.note</t>
   </si>
   <si>
@@ -1546,171 +1848,6 @@
   </si>
   <si>
     <t>ClinicalStatement.additionalText</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:finaliteExamen</t>
-  </si>
-  <si>
-    <t>finaliteExamen</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:finaliteExamen.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:finaliteExamen.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:finaliteExamen.extension:noteType</t>
-  </si>
-  <si>
-    <t>noteType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-note-type-extension|0.1.0}
-</t>
-  </si>
-  <si>
-    <t>FR Note Type Extension</t>
-  </si>
-  <si>
-    <t>Extension permettant de préciser le type d'information contenu dans une note associée à une demande d'examen d'imagerie.</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:finaliteExamen.extension:noteType.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note.extension.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:finaliteExamen.extension:noteType.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note.extension.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:finaliteExamen.extension:noteType.url</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note.extension.url</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-note-type-extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:finaliteExamen.extension:noteType.value[x]</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note.extension.value[x]</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-note-type|0.1.0</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:finaliteExamen.author[x]</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note.author[x]</t>
-  </si>
-  <si>
-    <t>Reference(Practitioner|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
-string</t>
-  </si>
-  <si>
-    <t>Individual responsible for the annotation</t>
-  </si>
-  <si>
-    <t>The individual responsible for making the annotation.</t>
-  </si>
-  <si>
-    <t>Organization is used when there's no need for specific attribution as to who made the comment.</t>
-  </si>
-  <si>
-    <t>Annotation.author[x]</t>
-  </si>
-  <si>
-    <t>Act.participant[typeCode=AUT].role</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:finaliteExamen.time</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note.time</t>
-  </si>
-  <si>
-    <t>When the annotation was made</t>
-  </si>
-  <si>
-    <t>Indicates when this particular annotation was made.</t>
-  </si>
-  <si>
-    <t>Annotation.time</t>
-  </si>
-  <si>
-    <t>Act.effectiveTime</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:finaliteExamen.text</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note.text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">markdown
-</t>
-  </si>
-  <si>
-    <t>The annotation  - text content (as markdown)</t>
-  </si>
-  <si>
-    <t>The text of the annotation in markdown format.</t>
-  </si>
-  <si>
-    <t>Annotation.text</t>
-  </si>
-  <si>
-    <t>Act.text</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:justificationDemande</t>
-  </si>
-  <si>
-    <t>justificationDemande</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:justificationDemande.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:justificationDemande.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:justificationDemande.extension:noteType</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:justificationDemande.extension:noteType.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:justificationDemande.extension:noteType.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:justificationDemande.extension:noteType.url</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:justificationDemande.extension:noteType.value[x]</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:justificationDemande.author[x]</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:justificationDemande.time</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note:justificationDemande.text</t>
   </si>
   <si>
     <t>ServiceRequest.patientInstruction</t>
@@ -2063,12 +2200,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO87"/>
+  <dimension ref="A1:AO114"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="58.80078125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="37.7265625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="17.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="1" max="1" width="74.65234375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="23.54296875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="37.7265625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -2093,7 +2230,7 @@
     <col min="25" max="25" width="160.17578125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="74.97265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="90.09765625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
@@ -3061,7 +3198,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>80</v>
@@ -5597,15 +5734,17 @@
         <v>207</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="D31" t="s" s="2">
-        <v>208</v>
+        <v>81</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>80</v>
@@ -5614,26 +5753,24 @@
         <v>81</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>135</v>
+        <v>209</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O31" t="s" s="2">
         <v>212</v>
       </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>81</v>
       </c>
@@ -5681,7 +5818,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>213</v>
+        <v>140</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5702,7 +5839,7 @@
         <v>81</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
@@ -5711,44 +5848,46 @@
         <v>81</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="C32" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="B32" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5786,17 +5925,19 @@
         <v>81</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="AC32" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>214</v>
+        <v>140</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5808,34 +5949,32 @@
         <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>221</v>
+        <v>81</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>222</v>
+        <v>81</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>223</v>
+        <v>81</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>81</v>
       </c>
@@ -5853,20 +5992,18 @@
         <v>81</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>227</v>
+        <v>155</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>228</v>
+        <v>156</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>218</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>81</v>
@@ -5915,42 +6052,42 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>214</v>
+        <v>158</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>221</v>
+        <v>81</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>222</v>
+        <v>159</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>223</v>
+        <v>81</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>229</v>
+        <v>161</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5958,7 +6095,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>80</v>
@@ -5970,20 +6107,18 @@
         <v>81</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>230</v>
+        <v>135</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>231</v>
+        <v>136</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>81</v>
@@ -6020,19 +6155,19 @@
         <v>81</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>229</v>
+        <v>164</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6044,16 +6179,16 @@
         <v>81</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>234</v>
+        <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>235</v>
+        <v>81</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>236</v>
+        <v>81</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>81</v>
@@ -6064,21 +6199,23 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="C35" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="D35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>81</v>
@@ -6087,20 +6224,18 @@
         <v>81</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>238</v>
+        <v>219</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -6149,7 +6284,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6161,16 +6296,16 @@
         <v>81</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>241</v>
+        <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>235</v>
+        <v>81</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>236</v>
+        <v>81</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
@@ -6181,21 +6316,21 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>242</v>
+        <v>221</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>242</v>
+        <v>168</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>81</v>
@@ -6204,16 +6339,16 @@
         <v>81</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>244</v>
+        <v>155</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>245</v>
+        <v>156</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>246</v>
+        <v>157</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6264,28 +6399,28 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>242</v>
+        <v>158</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>247</v>
+        <v>81</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>248</v>
+        <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>249</v>
+        <v>159</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
@@ -6296,14 +6431,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>250</v>
+        <v>222</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>251</v>
+        <v>223</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6319,18 +6454,20 @@
         <v>81</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>252</v>
+        <v>135</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>253</v>
+        <v>224</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -6367,19 +6504,19 @@
         <v>81</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>250</v>
+        <v>164</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6391,16 +6528,16 @@
         <v>81</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>255</v>
+        <v>81</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>256</v>
+        <v>81</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>257</v>
+        <v>159</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>81</v>
@@ -6411,18 +6548,18 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>258</v>
+        <v>227</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>258</v>
+        <v>172</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>259</v>
+        <v>81</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>90</v>
@@ -6434,29 +6571,27 @@
         <v>81</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>215</v>
+        <v>104</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>260</v>
+        <v>173</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>261</v>
+        <v>174</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>81</v>
+        <v>228</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>81</v>
@@ -6498,10 +6633,10 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>258</v>
+        <v>176</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>90</v>
@@ -6510,16 +6645,16 @@
         <v>81</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>264</v>
+        <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>265</v>
+        <v>81</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>266</v>
+        <v>133</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>81</v>
@@ -6530,10 +6665,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>267</v>
+        <v>229</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>267</v>
+        <v>178</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6550,22 +6685,22 @@
         <v>81</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>110</v>
+        <v>155</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>268</v>
+        <v>179</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>269</v>
+        <v>180</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>270</v>
+        <v>230</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6573,7 +6708,7 @@
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>81</v>
+        <v>231</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>81</v>
@@ -6591,13 +6726,13 @@
         <v>81</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>182</v>
+        <v>81</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>271</v>
+        <v>81</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>272</v>
+        <v>81</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>81</v>
@@ -6615,10 +6750,10 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>267</v>
+        <v>184</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>90</v>
@@ -6630,29 +6765,31 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>273</v>
+        <v>81</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>274</v>
+        <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>275</v>
+        <v>133</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>276</v>
+        <v>81</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>277</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>278</v>
+        <v>232</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="C40" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="D40" t="s" s="2">
         <v>81</v>
       </c>
@@ -6667,23 +6804,21 @@
         <v>91</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>279</v>
+        <v>136</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6708,13 +6843,13 @@
         <v>81</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>182</v>
+        <v>81</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>282</v>
+        <v>81</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>283</v>
+        <v>81</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
@@ -6732,42 +6867,42 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>278</v>
+        <v>164</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>284</v>
+        <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>285</v>
+        <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>286</v>
+        <v>81</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>287</v>
+        <v>234</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>287</v>
+        <v>168</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6778,32 +6913,28 @@
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>192</v>
+        <v>155</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>288</v>
+        <v>156</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>81</v>
       </c>
@@ -6827,13 +6958,13 @@
         <v>81</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>292</v>
+        <v>81</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>293</v>
+        <v>81</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>294</v>
+        <v>81</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>81</v>
@@ -6851,31 +6982,31 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>287</v>
+        <v>158</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>295</v>
+        <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>296</v>
+        <v>159</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>286</v>
+        <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>81</v>
@@ -6883,10 +7014,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>297</v>
+        <v>235</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>297</v>
+        <v>170</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6897,7 +7028,7 @@
         <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>81</v>
@@ -6906,25 +7037,23 @@
         <v>81</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>298</v>
+        <v>136</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>299</v>
+        <v>137</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q42" t="s" s="2">
-        <v>300</v>
-      </c>
+      <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
         <v>81</v>
       </c>
@@ -6944,55 +7073,55 @@
         <v>81</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>182</v>
+        <v>81</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>301</v>
+        <v>81</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>302</v>
+        <v>81</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>297</v>
+        <v>164</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>303</v>
+        <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>304</v>
+        <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>305</v>
+        <v>81</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>306</v>
+        <v>81</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>81</v>
@@ -7000,10 +7129,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>307</v>
+        <v>236</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>307</v>
+        <v>172</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7011,7 +7140,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>90</v>
@@ -7020,34 +7149,30 @@
         <v>81</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>308</v>
+        <v>104</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>309</v>
+        <v>173</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>310</v>
+        <v>174</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q43" t="s" s="2">
-        <v>313</v>
-      </c>
+      <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>81</v>
+        <v>233</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>81</v>
@@ -7089,10 +7214,10 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>307</v>
+        <v>176</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>90</v>
@@ -7101,16 +7226,16 @@
         <v>81</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>314</v>
+        <v>81</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>315</v>
+        <v>133</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>81</v>
@@ -7119,45 +7244,43 @@
         <v>81</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>316</v>
+        <v>237</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>316</v>
+        <v>178</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>317</v>
+        <v>81</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>192</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>318</v>
+        <v>238</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>320</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -7167,7 +7290,7 @@
         <v>81</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>81</v>
+        <v>240</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>81</v>
@@ -7182,13 +7305,13 @@
         <v>81</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>292</v>
+        <v>81</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>321</v>
+        <v>81</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>322</v>
+        <v>81</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>81</v>
@@ -7206,7 +7329,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>316</v>
+        <v>184</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7221,60 +7344,58 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>323</v>
+        <v>81</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>325</v>
+        <v>133</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>326</v>
+        <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>327</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>328</v>
+        <v>241</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>328</v>
+        <v>242</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>329</v>
+        <v>81</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>192</v>
+        <v>155</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>330</v>
+        <v>156</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>332</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -7299,13 +7420,13 @@
         <v>81</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>292</v>
+        <v>81</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>333</v>
+        <v>81</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>334</v>
+        <v>81</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
@@ -7323,53 +7444,53 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>328</v>
+        <v>158</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>335</v>
+        <v>81</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>336</v>
+        <v>81</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>325</v>
+        <v>159</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>327</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>337</v>
+        <v>243</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>337</v>
+        <v>244</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>81</v>
+        <v>223</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>81</v>
@@ -7378,21 +7499,21 @@
         <v>81</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>338</v>
+        <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>339</v>
+        <v>224</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>81</v>
       </c>
@@ -7428,40 +7549,40 @@
         <v>81</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>337</v>
+        <v>164</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>336</v>
+        <v>81</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>342</v>
+        <v>159</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -7472,10 +7593,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>343</v>
+        <v>245</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>343</v>
+        <v>246</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7483,10 +7604,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>81</v>
@@ -7498,16 +7619,20 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>344</v>
+        <v>247</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>345</v>
+        <v>248</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
       </c>
@@ -7555,13 +7680,13 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>343</v>
+        <v>252</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>81</v>
@@ -7570,41 +7695,41 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>347</v>
+        <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>348</v>
+        <v>253</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>349</v>
+        <v>254</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>350</v>
+        <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>351</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>352</v>
+        <v>255</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>352</v>
+        <v>256</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>353</v>
+        <v>81</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>81</v>
@@ -7613,16 +7738,20 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>354</v>
+        <v>155</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>355</v>
+        <v>257</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
       </c>
@@ -7670,7 +7799,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>352</v>
+        <v>261</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7685,59 +7814,65 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>357</v>
+        <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>358</v>
+        <v>262</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>359</v>
+        <v>263</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>360</v>
+        <v>81</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>361</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>362</v>
+        <v>264</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="C49" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="D49" t="s" s="2">
-        <v>363</v>
+        <v>81</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>364</v>
+        <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>365</v>
+        <v>266</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>81</v>
       </c>
@@ -7785,42 +7920,42 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>362</v>
+        <v>164</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>367</v>
+        <v>81</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>368</v>
+        <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>369</v>
+        <v>81</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>370</v>
+        <v>81</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>371</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>372</v>
+        <v>269</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>372</v>
+        <v>168</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7840,16 +7975,16 @@
         <v>81</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>373</v>
+        <v>155</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>374</v>
+        <v>156</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>375</v>
+        <v>157</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7876,13 +8011,13 @@
         <v>81</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>292</v>
+        <v>81</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>376</v>
+        <v>81</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>377</v>
+        <v>81</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
@@ -7900,7 +8035,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>372</v>
+        <v>158</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7912,7 +8047,7 @@
         <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>81</v>
@@ -7921,32 +8056,32 @@
         <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>378</v>
+        <v>159</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>379</v>
+        <v>81</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>380</v>
+        <v>270</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>380</v>
+        <v>170</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>381</v>
+        <v>223</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>81</v>
@@ -7955,18 +8090,20 @@
         <v>81</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>382</v>
+        <v>135</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>383</v>
+        <v>224</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>81</v>
@@ -8003,86 +8140,86 @@
         <v>81</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>380</v>
+        <v>164</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>385</v>
+        <v>81</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>386</v>
+        <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>387</v>
+        <v>159</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>388</v>
+        <v>81</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>389</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>390</v>
+        <v>271</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>390</v>
+        <v>172</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>391</v>
+        <v>81</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>392</v>
+        <v>104</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>393</v>
+        <v>173</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>394</v>
+        <v>174</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>395</v>
+        <v>175</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8090,7 +8227,7 @@
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>81</v>
+        <v>265</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>81</v>
@@ -8132,10 +8269,10 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>390</v>
+        <v>176</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>90</v>
@@ -8144,34 +8281,34 @@
         <v>81</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>396</v>
+        <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>397</v>
+        <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>398</v>
+        <v>133</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>399</v>
+        <v>81</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>400</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>401</v>
+        <v>272</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>401</v>
+        <v>178</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>402</v>
+        <v>81</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8187,20 +8324,18 @@
         <v>81</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>192</v>
+        <v>273</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>403</v>
+        <v>274</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>405</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -8225,13 +8360,13 @@
         <v>81</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>292</v>
+        <v>81</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>406</v>
+        <v>81</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>407</v>
+        <v>81</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>81</v>
@@ -8249,7 +8384,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>401</v>
+        <v>184</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8264,16 +8399,16 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>408</v>
+        <v>81</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>409</v>
+        <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>410</v>
+        <v>133</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>411</v>
+        <v>81</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>81</v>
@@ -8281,21 +8416,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>412</v>
+        <v>276</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>412</v>
+        <v>202</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>413</v>
+        <v>81</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>81</v>
@@ -8304,19 +8439,19 @@
         <v>81</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>414</v>
+        <v>104</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>415</v>
+        <v>173</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>416</v>
+        <v>174</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>417</v>
+        <v>175</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8324,7 +8459,7 @@
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>81</v>
+        <v>277</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>81</v>
@@ -8366,31 +8501,31 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>412</v>
+        <v>176</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>418</v>
+        <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>419</v>
+        <v>81</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>420</v>
+        <v>133</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>411</v>
+        <v>81</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>81</v>
@@ -8398,10 +8533,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>421</v>
+        <v>278</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>421</v>
+        <v>205</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8412,7 +8547,7 @@
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>81</v>
@@ -8421,16 +8556,16 @@
         <v>81</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>422</v>
+        <v>179</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>423</v>
+        <v>180</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8457,13 +8592,13 @@
         <v>81</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>292</v>
+        <v>81</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>424</v>
+        <v>81</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>425</v>
+        <v>81</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>81</v>
@@ -8481,13 +8616,13 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>421</v>
+        <v>184</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>81</v>
@@ -8502,23 +8637,25 @@
         <v>81</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>426</v>
+        <v>133</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>411</v>
+        <v>81</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>427</v>
+        <v>279</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="C56" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="C56" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="D56" t="s" s="2">
         <v>81</v>
       </c>
@@ -8527,27 +8664,29 @@
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>428</v>
+        <v>209</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>422</v>
+        <v>210</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8596,7 +8735,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>427</v>
+        <v>140</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8608,7 +8747,7 @@
         <v>81</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>81</v>
@@ -8617,10 +8756,10 @@
         <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>430</v>
+        <v>81</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>411</v>
+        <v>81</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>81</v>
@@ -8628,10 +8767,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>431</v>
+        <v>281</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>431</v>
+        <v>154</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8642,7 +8781,7 @@
         <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>81</v>
@@ -8651,20 +8790,18 @@
         <v>81</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>192</v>
+        <v>155</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>432</v>
+        <v>156</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>434</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>81</v>
@@ -8689,13 +8826,13 @@
         <v>81</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>292</v>
+        <v>81</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>435</v>
+        <v>81</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>436</v>
+        <v>81</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>81</v>
@@ -8713,31 +8850,31 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>431</v>
+        <v>158</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>437</v>
+        <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>438</v>
+        <v>81</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>439</v>
+        <v>159</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>440</v>
+        <v>81</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>81</v>
@@ -8745,10 +8882,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>441</v>
+        <v>282</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>441</v>
+        <v>161</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8756,7 +8893,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>80</v>
@@ -8768,20 +8905,18 @@
         <v>81</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>442</v>
+        <v>135</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>443</v>
+        <v>136</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>445</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -8818,19 +8953,19 @@
         <v>81</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>441</v>
+        <v>164</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8842,19 +8977,19 @@
         <v>81</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>446</v>
+        <v>81</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>447</v>
+        <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>448</v>
+        <v>81</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>440</v>
+        <v>81</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>81</v>
@@ -8862,21 +8997,23 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>449</v>
+        <v>283</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="D59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>81</v>
@@ -8888,13 +9025,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>450</v>
+        <v>135</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>451</v>
+        <v>219</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>452</v>
+        <v>220</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8945,7 +9082,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>449</v>
+        <v>164</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8957,16 +9094,16 @@
         <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>453</v>
+        <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>454</v>
+        <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>455</v>
+        <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>81</v>
@@ -8977,21 +9114,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>456</v>
+        <v>284</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>456</v>
+        <v>168</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>457</v>
+        <v>81</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>81</v>
@@ -9003,17 +9140,15 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>458</v>
+        <v>155</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>459</v>
+        <v>156</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>81</v>
@@ -9062,28 +9197,28 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>456</v>
+        <v>158</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>462</v>
+        <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>463</v>
+        <v>81</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>464</v>
+        <v>159</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>81</v>
@@ -9094,14 +9229,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>465</v>
+        <v>285</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>465</v>
+        <v>170</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>81</v>
+        <v>223</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9117,19 +9252,19 @@
         <v>81</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>466</v>
+        <v>135</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>467</v>
+        <v>224</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>468</v>
+        <v>225</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>469</v>
+        <v>226</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9167,19 +9302,19 @@
         <v>81</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>465</v>
+        <v>164</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9191,16 +9326,16 @@
         <v>81</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>470</v>
+        <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>471</v>
+        <v>159</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>81</v>
@@ -9209,54 +9344,52 @@
         <v>81</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>472</v>
+        <v>286</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>472</v>
+        <v>172</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>473</v>
+        <v>81</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>192</v>
+        <v>104</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>474</v>
+        <v>173</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>475</v>
+        <v>174</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>477</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>81</v>
+        <v>228</v>
       </c>
       <c r="S62" t="s" s="2">
         <v>81</v>
@@ -9274,11 +9407,13 @@
         <v>81</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="Y62" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z62" t="s" s="2">
-        <v>479</v>
+        <v>81</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>81</v>
@@ -9296,42 +9431,42 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>472</v>
+        <v>176</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>470</v>
+        <v>81</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>480</v>
+        <v>133</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>481</v>
+        <v>81</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>482</v>
+        <v>287</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>482</v>
+        <v>178</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9342,10 +9477,10 @@
         <v>90</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>81</v>
@@ -9354,22 +9489,24 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>483</v>
+        <v>155</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>484</v>
+        <v>179</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q63" s="2"/>
       <c r="R63" t="s" s="2">
-        <v>81</v>
+        <v>231</v>
       </c>
       <c r="S63" t="s" s="2">
         <v>81</v>
@@ -9399,23 +9536,25 @@
         <v>81</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="AC63" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>482</v>
+        <v>184</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>81</v>
@@ -9424,30 +9563,30 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>487</v>
+        <v>81</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>336</v>
+        <v>81</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>488</v>
+        <v>133</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>489</v>
+        <v>81</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>490</v>
+        <v>288</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>482</v>
+        <v>161</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>491</v>
+        <v>233</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>81</v>
@@ -9469,13 +9608,13 @@
         <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>483</v>
+        <v>135</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>484</v>
+        <v>136</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>485</v>
+        <v>137</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9526,7 +9665,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>482</v>
+        <v>164</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9538,30 +9677,30 @@
         <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>487</v>
+        <v>81</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>336</v>
+        <v>81</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>488</v>
+        <v>81</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>489</v>
+        <v>81</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>492</v>
+        <v>289</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>493</v>
+        <v>168</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9673,10 +9812,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>494</v>
+        <v>290</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>495</v>
+        <v>170</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9684,10 +9823,10 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>81</v>
@@ -9786,16 +9925,14 @@
         <v>81</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>496</v>
+        <v>291</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>497</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>81</v>
       </c>
@@ -9807,7 +9944,7 @@
         <v>90</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>81</v>
@@ -9816,22 +9953,24 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>498</v>
+        <v>104</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>499</v>
+        <v>173</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>81</v>
+        <v>233</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>81</v>
@@ -9873,19 +10012,19 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>81</v>
@@ -9894,7 +10033,7 @@
         <v>81</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>81</v>
@@ -9905,10 +10044,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>501</v>
+        <v>292</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>502</v>
+        <v>178</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9931,13 +10070,13 @@
         <v>81</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>156</v>
+        <v>238</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>157</v>
+        <v>239</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9949,7 +10088,7 @@
         <v>81</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>81</v>
+        <v>293</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>81</v>
@@ -9988,7 +10127,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10000,7 +10139,7 @@
         <v>81</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>81</v>
@@ -10009,7 +10148,7 @@
         <v>81</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>81</v>
@@ -10020,10 +10159,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>503</v>
+        <v>294</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>504</v>
+        <v>242</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10034,7 +10173,7 @@
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>81</v>
@@ -10046,13 +10185,13 @@
         <v>81</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10091,31 +10230,31 @@
         <v>81</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>81</v>
@@ -10124,7 +10263,7 @@
         <v>81</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>81</v>
+        <v>159</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>81</v>
@@ -10135,21 +10274,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>505</v>
+        <v>295</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>506</v>
+        <v>244</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>81</v>
+        <v>223</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>81</v>
@@ -10161,16 +10300,16 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>173</v>
+        <v>224</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>174</v>
+        <v>225</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>175</v>
+        <v>226</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10178,7 +10317,7 @@
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>507</v>
+        <v>81</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>81</v>
@@ -10208,31 +10347,31 @@
         <v>81</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>81</v>
@@ -10241,7 +10380,7 @@
         <v>81</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>81</v>
@@ -10252,10 +10391,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>508</v>
+        <v>296</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>509</v>
+        <v>246</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10266,7 +10405,7 @@
         <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>81</v>
@@ -10275,19 +10414,23 @@
         <v>81</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>110</v>
+        <v>247</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>179</v>
+        <v>248</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>81</v>
       </c>
@@ -10296,7 +10439,7 @@
         <v>81</v>
       </c>
       <c r="S71" t="s" s="2">
-        <v>491</v>
+        <v>81</v>
       </c>
       <c r="T71" t="s" s="2">
         <v>81</v>
@@ -10311,11 +10454,13 @@
         <v>81</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Y71" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z71" t="s" s="2">
-        <v>510</v>
+        <v>81</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>81</v>
@@ -10333,13 +10478,13 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>184</v>
+        <v>252</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>81</v>
@@ -10351,10 +10496,10 @@
         <v>81</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>81</v>
+        <v>253</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>133</v>
+        <v>254</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
@@ -10363,12 +10508,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
-        <v>511</v>
+        <v>297</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>512</v>
+        <v>256</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10376,13 +10521,13 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>81</v>
@@ -10391,18 +10536,20 @@
         <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>513</v>
+        <v>155</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>514</v>
+        <v>257</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>515</v>
+        <v>258</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="O72" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
       </c>
@@ -10450,7 +10597,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>517</v>
+        <v>261</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10468,10 +10615,10 @@
         <v>81</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>133</v>
+        <v>262</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>518</v>
+        <v>263</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>81</v>
@@ -10482,12 +10629,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>519</v>
+        <v>298</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="C73" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="C73" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="D73" t="s" s="2">
         <v>81</v>
       </c>
@@ -10505,19 +10654,23 @@
         <v>81</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>382</v>
+        <v>135</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>521</v>
+        <v>266</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>81</v>
       </c>
@@ -10565,28 +10718,28 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>523</v>
+        <v>164</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>524</v>
+        <v>81</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>81</v>
@@ -10597,10 +10750,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>525</v>
+        <v>299</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>526</v>
+        <v>168</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10608,7 +10761,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>90</v>
@@ -10620,16 +10773,16 @@
         <v>81</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>527</v>
+        <v>155</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>528</v>
+        <v>156</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>529</v>
+        <v>157</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10680,10 +10833,10 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>530</v>
+        <v>158</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>90</v>
@@ -10692,16 +10845,16 @@
         <v>81</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>531</v>
+        <v>159</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>81</v>
@@ -10710,28 +10863,26 @@
         <v>81</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>532</v>
+        <v>300</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="C75" t="s" s="2">
-        <v>533</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>81</v>
+        <v>223</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>81</v>
@@ -10740,15 +10891,17 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>483</v>
+        <v>135</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>484</v>
+        <v>224</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>81</v>
@@ -10785,19 +10938,19 @@
         <v>81</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>482</v>
+        <v>164</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10809,30 +10962,30 @@
         <v>81</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>487</v>
+        <v>81</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>336</v>
+        <v>81</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>488</v>
+        <v>159</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>489</v>
+        <v>81</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>534</v>
+        <v>301</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>493</v>
+        <v>172</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10840,7 +10993,7 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>90</v>
@@ -10855,22 +11008,24 @@
         <v>81</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>155</v>
+        <v>104</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
-        <v>81</v>
+        <v>265</v>
       </c>
       <c r="S76" t="s" s="2">
         <v>81</v>
@@ -10912,10 +11067,10 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>90</v>
@@ -10933,7 +11088,7 @@
         <v>81</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>81</v>
@@ -10944,10 +11099,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>535</v>
+        <v>302</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>495</v>
+        <v>178</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10955,10 +11110,10 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>81</v>
@@ -10970,13 +11125,13 @@
         <v>81</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>135</v>
+        <v>273</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>136</v>
+        <v>274</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>137</v>
+        <v>275</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11015,31 +11170,31 @@
         <v>81</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>81</v>
@@ -11048,7 +11203,7 @@
         <v>81</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>81</v>
@@ -11057,16 +11212,14 @@
         <v>81</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>536</v>
+        <v>303</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="C78" t="s" s="2">
-        <v>497</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>81</v>
       </c>
@@ -11078,7 +11231,7 @@
         <v>90</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>81</v>
@@ -11087,22 +11240,24 @@
         <v>81</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>498</v>
+        <v>104</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>499</v>
+        <v>173</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q78" s="2"/>
       <c r="R78" t="s" s="2">
-        <v>81</v>
+        <v>277</v>
       </c>
       <c r="S78" t="s" s="2">
         <v>81</v>
@@ -11144,19 +11299,19 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>81</v>
@@ -11165,7 +11320,7 @@
         <v>81</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>81</v>
@@ -11176,10 +11331,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>537</v>
+        <v>304</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>502</v>
+        <v>205</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11190,7 +11345,7 @@
         <v>79</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>81</v>
@@ -11202,13 +11357,13 @@
         <v>81</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>155</v>
+        <v>206</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11259,7 +11414,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11271,7 +11426,7 @@
         <v>81</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>81</v>
@@ -11280,7 +11435,7 @@
         <v>81</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>81</v>
@@ -11291,27 +11446,27 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>538</v>
+        <v>305</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>504</v>
+        <v>305</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>81</v>
+        <v>223</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J80" t="s" s="2">
         <v>81</v>
@@ -11320,13 +11475,17 @@
         <v>135</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>136</v>
+        <v>306</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>81</v>
       </c>
@@ -11362,19 +11521,19 @@
         <v>81</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>164</v>
+        <v>309</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11395,7 +11554,7 @@
         <v>81</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>81</v>
@@ -11406,10 +11565,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>539</v>
+        <v>310</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>506</v>
+        <v>310</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11417,10 +11576,10 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>81</v>
@@ -11429,19 +11588,19 @@
         <v>81</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>104</v>
+        <v>311</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>173</v>
+        <v>312</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>174</v>
+        <v>313</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>175</v>
+        <v>314</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11449,7 +11608,7 @@
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
-        <v>507</v>
+        <v>81</v>
       </c>
       <c r="S81" t="s" s="2">
         <v>81</v>
@@ -11479,56 +11638,56 @@
         <v>81</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="AC81" s="2"/>
       <c r="AD81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>176</v>
+        <v>310</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>81</v>
+        <v>316</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>81</v>
+        <v>317</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>133</v>
+        <v>318</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>81</v>
+        <v>319</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>81</v>
+        <v>320</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>540</v>
+        <v>321</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="C82" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="C82" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="D82" t="s" s="2">
         <v>81</v>
       </c>
@@ -11546,18 +11705,20 @@
         <v>81</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>110</v>
+        <v>323</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>179</v>
+        <v>324</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>313</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>314</v>
+      </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -11567,7 +11728,7 @@
         <v>81</v>
       </c>
       <c r="S82" t="s" s="2">
-        <v>533</v>
+        <v>81</v>
       </c>
       <c r="T82" t="s" s="2">
         <v>81</v>
@@ -11582,11 +11743,13 @@
         <v>81</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Y82" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z82" t="s" s="2">
-        <v>510</v>
+        <v>81</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>81</v>
@@ -11604,13 +11767,13 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>184</v>
+        <v>310</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>81</v>
@@ -11619,27 +11782,27 @@
         <v>102</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>81</v>
+        <v>316</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>81</v>
+        <v>317</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>133</v>
+        <v>318</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>81</v>
+        <v>319</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>81</v>
+        <v>320</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>541</v>
+        <v>325</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>512</v>
+        <v>325</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11650,7 +11813,7 @@
         <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>81</v>
@@ -11662,16 +11825,16 @@
         <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>513</v>
+        <v>326</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>514</v>
+        <v>327</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>515</v>
+        <v>328</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>516</v>
+        <v>329</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11721,13 +11884,13 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>517</v>
+        <v>325</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>81</v>
@@ -11736,13 +11899,13 @@
         <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>81</v>
+        <v>330</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>133</v>
+        <v>331</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>518</v>
+        <v>332</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>81</v>
@@ -11753,10 +11916,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>542</v>
+        <v>333</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>520</v>
+        <v>333</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11767,7 +11930,7 @@
         <v>79</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>81</v>
@@ -11779,15 +11942,17 @@
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>382</v>
+        <v>104</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>521</v>
+        <v>334</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -11836,13 +12001,13 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>523</v>
+        <v>333</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>81</v>
@@ -11851,13 +12016,13 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>81</v>
+        <v>337</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>133</v>
+        <v>331</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>524</v>
+        <v>332</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>81</v>
@@ -11868,21 +12033,21 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>543</v>
+        <v>338</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>526</v>
+        <v>338</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>81</v>
+        <v>339</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>81</v>
@@ -11894,13 +12059,13 @@
         <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>527</v>
+        <v>340</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>528</v>
+        <v>341</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>529</v>
+        <v>342</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11951,13 +12116,13 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>530</v>
+        <v>338</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>81</v>
@@ -11966,13 +12131,13 @@
         <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>81</v>
+        <v>343</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>133</v>
+        <v>344</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>531</v>
+        <v>345</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>81</v>
@@ -11983,21 +12148,21 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>544</v>
+        <v>346</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>544</v>
+        <v>346</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>81</v>
+        <v>347</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>81</v>
@@ -12009,13 +12174,13 @@
         <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>155</v>
+        <v>348</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>545</v>
+        <v>349</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>546</v>
+        <v>350</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12066,13 +12231,13 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>544</v>
+        <v>346</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>81</v>
@@ -12081,13 +12246,13 @@
         <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>81</v>
+        <v>351</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>547</v>
+        <v>353</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>81</v>
@@ -12098,21 +12263,21 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>548</v>
+        <v>354</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>548</v>
+        <v>354</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>81</v>
+        <v>355</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>81</v>
@@ -12121,21 +12286,23 @@
         <v>81</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>549</v>
+        <v>311</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>550</v>
+        <v>356</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>551</v>
+        <v>357</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="O87" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>81</v>
       </c>
@@ -12183,13 +12350,13 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>548</v>
+        <v>354</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>81</v>
@@ -12198,23 +12365,3168 @@
         <v>102</v>
       </c>
       <c r="AK87" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AO88" t="s" s="2">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="P90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AO90" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
+      <c r="P91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q91" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="R91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AO91" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="P92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q92" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="R92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="O94" s="2"/>
+      <c r="P94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="P95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
+      <c r="P97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
+      <c r="P98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" s="2"/>
+      <c r="P99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" s="2"/>
+      <c r="P100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="105" hidden="true">
+      <c r="A105" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="N105" s="2"/>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="O106" s="2"/>
+      <c r="P106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="107" hidden="true">
+      <c r="A107" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="O107" s="2"/>
+      <c r="P107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="108" hidden="true">
+      <c r="A108" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" s="2"/>
+      <c r="P108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="109" hidden="true">
+      <c r="A109" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="AL87" t="s" s="2">
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="O109" s="2"/>
+      <c r="P109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO109" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="110" hidden="true">
+      <c r="A110" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="O110" s="2"/>
+      <c r="P110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO110" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="P111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="Y111" s="2"/>
+      <c r="Z111" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO111" t="s" s="2">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" s="2"/>
+      <c r="P112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO112" t="s" s="2">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="113" hidden="true">
+      <c r="A113" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" s="2"/>
+      <c r="P113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO113" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="O114" s="2"/>
+      <c r="P114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AL114" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="AM87" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO87" t="s" s="2">
+      <c r="AM114" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO114" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO87">
+  <autoFilter ref="A1:AO114">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12224,7 +15536,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI86">
+  <conditionalFormatting sqref="A2:AI113">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T12:56:12+00:00</t>
+    <t>2026-08-07T08:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:15:28+00:00</t>
+    <t>2026-08-07T09:41:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T09:41:31+00:00</t>
+    <t>2026-08-07T12:53:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T12:53:43+00:00</t>
+    <t>2026-09-03T14:46:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5827,7 +5827,7 @@
         <v>80</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>141</v>
@@ -5946,7 +5946,7 @@
         <v>80</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>141</v>
@@ -8744,7 +8744,7 @@
         <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>141</v>

--- a/main/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T14:46:57+00:00</t>
+    <t>2026-09-04T09:26:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:26:41+00:00</t>
+    <t>2026-09-04T11:53:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
